--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.72090607967326</v>
+        <v>4.179647237946904</v>
       </c>
       <c r="D2" t="n">
-        <v>25.74773887767818</v>
+        <v>4.184007567622706</v>
       </c>
       <c r="E2" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F2" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.47662429559382</v>
+        <v>5.114951448033996</v>
       </c>
       <c r="D3" t="n">
-        <v>33.83976252606754</v>
+        <v>5.498961410485975</v>
       </c>
       <c r="E3" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F3" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.78918387015806</v>
+        <v>7.440742378900684</v>
       </c>
       <c r="D4" t="n">
-        <v>46.8254555947718</v>
+        <v>7.609136534150417</v>
       </c>
       <c r="E4" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F4" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.44755515752805</v>
+        <v>7.710227713098308</v>
       </c>
       <c r="D5" t="n">
-        <v>47.1686260395584</v>
+        <v>7.66490173142824</v>
       </c>
       <c r="E5" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F5" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.12575235708817</v>
+        <v>3.595434758026828</v>
       </c>
       <c r="D6" t="n">
-        <v>21.68629442162245</v>
+        <v>3.524022843513649</v>
       </c>
       <c r="E6" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F6" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.53314111388504</v>
+        <v>8.86163543100632</v>
       </c>
       <c r="D7" t="n">
-        <v>55.3391167617335</v>
+        <v>8.992606473781693</v>
       </c>
       <c r="E7" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F7" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.10210167096294</v>
+        <v>5.704091521531478</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29011562573111</v>
+        <v>5.572143789181306</v>
       </c>
       <c r="E8" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F8" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.90635139212861</v>
+        <v>3.234782101220899</v>
       </c>
       <c r="D9" t="n">
-        <v>18.97408362067389</v>
+        <v>3.083288588359507</v>
       </c>
       <c r="E9" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F9" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.15768336142406</v>
+        <v>7.663123546231409</v>
       </c>
       <c r="D10" t="n">
-        <v>47.78636986711758</v>
+        <v>7.765285103406606</v>
       </c>
       <c r="E10" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F10" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.9645124621849</v>
+        <v>6.819233275105046</v>
       </c>
       <c r="D11" t="n">
-        <v>42.3995632698525</v>
+        <v>6.889929031351032</v>
       </c>
       <c r="E11" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F11" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.77000543476956</v>
+        <v>5.650125883150054</v>
       </c>
       <c r="D12" t="n">
-        <v>33.75406041131532</v>
+        <v>5.485034816838739</v>
       </c>
       <c r="E12" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F12" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.70558654857249</v>
+        <v>6.93965781414303</v>
       </c>
       <c r="D13" t="n">
-        <v>42.86756496419797</v>
+        <v>6.96597930668217</v>
       </c>
       <c r="E13" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F13" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.91688818597907</v>
+        <v>5.186494330221599</v>
       </c>
       <c r="D14" t="n">
-        <v>32.07786344576984</v>
+        <v>5.212652809937598</v>
       </c>
       <c r="E14" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F14" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.40202938780383</v>
+        <v>5.102829775518122</v>
       </c>
       <c r="D15" t="n">
-        <v>57.93893142243196</v>
+        <v>9.415076356145194</v>
       </c>
       <c r="E15" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F15" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>13.72223028851972</v>
+        <v>2.229862421884454</v>
       </c>
       <c r="D16" t="n">
-        <v>13.83771946402581</v>
+        <v>2.248629412904195</v>
       </c>
       <c r="E16" t="n">
-        <v>11.18297199433831</v>
+        <v>1.817232949079975</v>
       </c>
       <c r="F16" t="n">
-        <v>12.72598241488573</v>
+        <v>2.067972142418931</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
